--- a/Milestone1SE.xlsx
+++ b/Milestone1SE.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635"/>
   </bookViews>
   <sheets>
     <sheet name="Team Info" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="402">
   <si>
     <t>Team Name</t>
   </si>
@@ -1285,6 +1285,24 @@
   </si>
   <si>
     <t>T-11</t>
+  </si>
+  <si>
+    <t>63-64-65</t>
+  </si>
+  <si>
+    <t>66-67</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - </t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>3-39-64-91-112</t>
+  </si>
+  <si>
+    <t>7-41-31-32-58</t>
   </si>
 </sst>
 </file>
@@ -3112,7 +3130,9 @@
       <c r="A5" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="9">
+        <v>2</v>
+      </c>
       <c r="C5" s="26">
         <v>3</v>
       </c>
@@ -3134,7 +3154,9 @@
       <c r="A6" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B6" s="9">
+        <v>3</v>
+      </c>
       <c r="C6" s="26">
         <v>4</v>
       </c>
@@ -3156,7 +3178,9 @@
       <c r="A7" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B7" s="9"/>
+      <c r="B7" s="9">
+        <v>3</v>
+      </c>
       <c r="C7" s="26">
         <v>5</v>
       </c>
@@ -3178,7 +3202,9 @@
       <c r="A8" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="9"/>
+      <c r="B8" s="9">
+        <v>2</v>
+      </c>
       <c r="C8" s="26">
         <v>6</v>
       </c>
@@ -3200,7 +3226,9 @@
       <c r="A9" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="9"/>
+      <c r="B9" s="9">
+        <v>2</v>
+      </c>
       <c r="C9" s="26">
         <v>7</v>
       </c>
@@ -3222,7 +3250,9 @@
       <c r="A10" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B10" s="9"/>
+      <c r="B10" s="9">
+        <v>2</v>
+      </c>
       <c r="C10" s="26">
         <v>8</v>
       </c>
@@ -3244,7 +3274,9 @@
       <c r="A11" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B11" s="9"/>
+      <c r="B11" s="9">
+        <v>8</v>
+      </c>
       <c r="C11" s="26">
         <v>9</v>
       </c>
@@ -3268,7 +3300,9 @@
       <c r="A12" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B12" s="9"/>
+      <c r="B12" s="9">
+        <v>2</v>
+      </c>
       <c r="C12" s="26">
         <v>10</v>
       </c>
@@ -3290,7 +3324,9 @@
       <c r="A13" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B13" s="9"/>
+      <c r="B13" s="9">
+        <v>2</v>
+      </c>
       <c r="C13" s="26">
         <v>11</v>
       </c>
@@ -3312,7 +3348,9 @@
       <c r="A14" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B14" s="9"/>
+      <c r="B14" s="9">
+        <v>11</v>
+      </c>
       <c r="C14" s="26">
         <v>12</v>
       </c>
@@ -3334,7 +3372,9 @@
       <c r="A15" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B15" s="9"/>
+      <c r="B15" s="9">
+        <v>12</v>
+      </c>
       <c r="C15" s="26">
         <v>13</v>
       </c>
@@ -3356,7 +3396,9 @@
       <c r="A16" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B16" s="9"/>
+      <c r="B16" s="9">
+        <v>13</v>
+      </c>
       <c r="C16" s="26">
         <v>14</v>
       </c>
@@ -3378,7 +3420,9 @@
       <c r="A17" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="B17" s="9"/>
+      <c r="B17" s="9">
+        <v>14</v>
+      </c>
       <c r="C17" s="26">
         <v>15</v>
       </c>
@@ -3400,7 +3444,9 @@
       <c r="A18" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="B18" s="9"/>
+      <c r="B18" s="9">
+        <v>15</v>
+      </c>
       <c r="C18" s="26">
         <v>16</v>
       </c>
@@ -3422,7 +3468,9 @@
       <c r="A19" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B19" s="9"/>
+      <c r="B19" s="9">
+        <v>16</v>
+      </c>
       <c r="C19" s="26">
         <v>17</v>
       </c>
@@ -3444,7 +3492,9 @@
       <c r="A20" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B20" s="9"/>
+      <c r="B20" s="9">
+        <v>17</v>
+      </c>
       <c r="C20" s="26">
         <v>18</v>
       </c>
@@ -3466,7 +3516,9 @@
       <c r="A21" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B21" s="9"/>
+      <c r="B21" s="9">
+        <v>17</v>
+      </c>
       <c r="C21" s="26">
         <v>19</v>
       </c>
@@ -3488,7 +3540,9 @@
       <c r="A22" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B22" s="9"/>
+      <c r="B22" s="9">
+        <v>9</v>
+      </c>
       <c r="C22" s="26">
         <v>20</v>
       </c>
@@ -3512,7 +3566,9 @@
       <c r="A23" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B23" s="9"/>
+      <c r="B23" s="9">
+        <v>2</v>
+      </c>
       <c r="C23" s="26">
         <v>21</v>
       </c>
@@ -3534,7 +3590,9 @@
       <c r="A24" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B24" s="9"/>
+      <c r="B24" s="9">
+        <v>2</v>
+      </c>
       <c r="C24" s="26">
         <v>22</v>
       </c>
@@ -3556,7 +3614,9 @@
       <c r="A25" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B25" s="9"/>
+      <c r="B25" s="9">
+        <v>3</v>
+      </c>
       <c r="C25" s="26">
         <v>23</v>
       </c>
@@ -3578,7 +3638,9 @@
       <c r="A26" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B26" s="9"/>
+      <c r="B26" s="9">
+        <v>3</v>
+      </c>
       <c r="C26" s="26">
         <v>24</v>
       </c>
@@ -3600,7 +3662,9 @@
       <c r="A27" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B27" s="9"/>
+      <c r="B27" s="9">
+        <v>23</v>
+      </c>
       <c r="C27" s="26">
         <v>25</v>
       </c>
@@ -3622,7 +3686,9 @@
       <c r="A28" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B28" s="9"/>
+      <c r="B28" s="9">
+        <v>2</v>
+      </c>
       <c r="C28" s="26">
         <v>26</v>
       </c>
@@ -3644,7 +3710,9 @@
       <c r="A29" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B29" s="9"/>
+      <c r="B29" s="9">
+        <v>2</v>
+      </c>
       <c r="C29" s="26">
         <v>27</v>
       </c>
@@ -3666,7 +3734,9 @@
       <c r="A30" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="9"/>
+      <c r="B30" s="9">
+        <v>2</v>
+      </c>
       <c r="C30" s="26">
         <v>28</v>
       </c>
@@ -3688,7 +3758,9 @@
       <c r="A31" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B31" s="9"/>
+      <c r="B31" s="9">
+        <v>24</v>
+      </c>
       <c r="C31" s="26">
         <v>29</v>
       </c>
@@ -3710,7 +3782,9 @@
       <c r="A32" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B32" s="9"/>
+      <c r="B32" s="9">
+        <v>17</v>
+      </c>
       <c r="C32" s="26">
         <v>30</v>
       </c>
@@ -3732,7 +3806,9 @@
       <c r="A33" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B33" s="9"/>
+      <c r="B33" s="9">
+        <v>17</v>
+      </c>
       <c r="C33" s="26">
         <v>31</v>
       </c>
@@ -3754,7 +3830,9 @@
       <c r="A34" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B34" s="9"/>
+      <c r="B34" s="9">
+        <v>31</v>
+      </c>
       <c r="C34" s="26">
         <v>32</v>
       </c>
@@ -3776,7 +3854,9 @@
       <c r="A35" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B35" s="9"/>
+      <c r="B35" s="9">
+        <v>32</v>
+      </c>
       <c r="C35" s="26">
         <v>33</v>
       </c>
@@ -3798,7 +3878,9 @@
       <c r="A36" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B36" s="9"/>
+      <c r="B36" s="9">
+        <v>30</v>
+      </c>
       <c r="C36" s="26">
         <v>34</v>
       </c>
@@ -3820,7 +3902,9 @@
       <c r="A37" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B37" s="9"/>
+      <c r="B37" s="9">
+        <v>32</v>
+      </c>
       <c r="C37" s="26">
         <v>35</v>
       </c>
@@ -3844,7 +3928,9 @@
       <c r="A38" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B38" s="9"/>
+      <c r="B38" s="9">
+        <v>2</v>
+      </c>
       <c r="C38" s="26">
         <v>36</v>
       </c>
@@ -3866,7 +3952,9 @@
       <c r="A39" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B39" s="9"/>
+      <c r="B39" s="9">
+        <v>2</v>
+      </c>
       <c r="C39" s="26">
         <v>37</v>
       </c>
@@ -3888,7 +3976,9 @@
       <c r="A40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="9"/>
+      <c r="B40" s="9">
+        <v>2</v>
+      </c>
       <c r="C40" s="26">
         <v>38</v>
       </c>
@@ -3910,7 +4000,9 @@
       <c r="A41" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="9"/>
+      <c r="B41" s="9">
+        <v>2</v>
+      </c>
       <c r="C41" s="26">
         <v>39</v>
       </c>
@@ -3932,7 +4024,9 @@
       <c r="A42" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B42" s="9"/>
+      <c r="B42" s="9">
+        <v>2</v>
+      </c>
       <c r="C42" s="26">
         <v>40</v>
       </c>
@@ -3954,7 +4048,9 @@
       <c r="A43" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B43" s="9"/>
+      <c r="B43" s="9">
+        <v>2</v>
+      </c>
       <c r="C43" s="26">
         <v>41</v>
       </c>
@@ -3976,7 +4072,9 @@
       <c r="A44" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="9"/>
+      <c r="B44" s="9">
+        <v>2</v>
+      </c>
       <c r="C44" s="26">
         <v>42</v>
       </c>
@@ -3998,7 +4096,9 @@
       <c r="A45" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B45" s="9"/>
+      <c r="B45" s="9">
+        <v>2</v>
+      </c>
       <c r="C45" s="26">
         <v>43</v>
       </c>
@@ -4022,7 +4122,9 @@
       <c r="A46" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B46" s="9"/>
+      <c r="B46" s="9">
+        <v>43</v>
+      </c>
       <c r="C46" s="26">
         <v>44</v>
       </c>
@@ -4044,7 +4146,9 @@
       <c r="A47" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B47" s="9"/>
+      <c r="B47" s="9">
+        <v>2</v>
+      </c>
       <c r="C47" s="26">
         <v>45</v>
       </c>
@@ -4066,7 +4170,9 @@
       <c r="A48" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="9"/>
+      <c r="B48" s="9">
+        <v>2</v>
+      </c>
       <c r="C48" s="26">
         <v>46</v>
       </c>
@@ -4088,7 +4194,9 @@
       <c r="A49" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="9"/>
+      <c r="B49" s="9">
+        <v>2</v>
+      </c>
       <c r="C49" s="26">
         <v>47</v>
       </c>
@@ -4110,7 +4218,9 @@
       <c r="A50" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B50" s="9"/>
+      <c r="B50" s="9">
+        <v>2</v>
+      </c>
       <c r="C50" s="26">
         <v>48</v>
       </c>
@@ -4132,7 +4242,9 @@
       <c r="A51" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="9"/>
+      <c r="B51" s="9">
+        <v>41</v>
+      </c>
       <c r="C51" s="26">
         <v>49</v>
       </c>
@@ -4154,7 +4266,9 @@
       <c r="A52" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B52" s="9"/>
+      <c r="B52" s="9">
+        <v>26</v>
+      </c>
       <c r="C52" s="26">
         <v>50</v>
       </c>
@@ -4176,7 +4290,9 @@
       <c r="A53" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="9"/>
+      <c r="B53" s="9">
+        <v>2</v>
+      </c>
       <c r="C53" s="26">
         <v>51</v>
       </c>
@@ -4198,7 +4314,9 @@
       <c r="A54" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="9"/>
+      <c r="B54" s="9">
+        <v>2</v>
+      </c>
       <c r="C54" s="26">
         <v>52</v>
       </c>
@@ -4220,7 +4338,9 @@
       <c r="A55" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B55" s="9"/>
+      <c r="B55" s="9">
+        <v>26</v>
+      </c>
       <c r="C55" s="26">
         <v>53</v>
       </c>
@@ -4242,7 +4362,9 @@
       <c r="A56" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B56" s="9"/>
+      <c r="B56" s="9">
+        <v>2</v>
+      </c>
       <c r="C56" s="26">
         <v>54</v>
       </c>
@@ -4264,7 +4386,9 @@
       <c r="A57" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B57" s="9"/>
+      <c r="B57" s="9">
+        <v>2</v>
+      </c>
       <c r="C57" s="26">
         <v>55</v>
       </c>
@@ -4286,7 +4410,9 @@
       <c r="A58" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="9"/>
+      <c r="B58" s="9">
+        <v>2</v>
+      </c>
       <c r="C58" s="26">
         <v>56</v>
       </c>
@@ -4308,7 +4434,9 @@
       <c r="A59" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B59" s="9"/>
+      <c r="B59" s="9">
+        <v>2</v>
+      </c>
       <c r="C59" s="26">
         <v>57</v>
       </c>
@@ -4330,7 +4458,9 @@
       <c r="A60" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B60" s="9"/>
+      <c r="B60" s="9">
+        <v>2</v>
+      </c>
       <c r="C60" s="26">
         <v>58</v>
       </c>
@@ -4352,7 +4482,9 @@
       <c r="A61" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B61" s="9"/>
+      <c r="B61" s="9">
+        <v>2</v>
+      </c>
       <c r="C61" s="26">
         <v>59</v>
       </c>
@@ -4374,7 +4506,9 @@
       <c r="A62" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B62" s="9"/>
+      <c r="B62" s="9">
+        <v>2</v>
+      </c>
       <c r="C62" s="26">
         <v>60</v>
       </c>
@@ -4396,7 +4530,9 @@
       <c r="A63" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B63" s="9"/>
+      <c r="B63" s="9">
+        <v>57</v>
+      </c>
       <c r="C63" s="26">
         <v>61</v>
       </c>
@@ -4418,7 +4554,9 @@
       <c r="A64" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B64" s="9"/>
+      <c r="B64" s="9">
+        <v>62</v>
+      </c>
       <c r="C64" s="26">
         <v>62</v>
       </c>
@@ -4440,7 +4578,9 @@
       <c r="A65" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B65" s="9"/>
+      <c r="B65" s="9">
+        <v>62</v>
+      </c>
       <c r="C65" s="26">
         <v>63</v>
       </c>
@@ -4462,7 +4602,9 @@
       <c r="A66" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B66" s="9"/>
+      <c r="B66" s="9">
+        <v>62</v>
+      </c>
       <c r="C66" s="26">
         <v>64</v>
       </c>
@@ -4484,7 +4626,9 @@
       <c r="A67" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B67" s="9"/>
+      <c r="B67" s="9">
+        <v>62</v>
+      </c>
       <c r="C67" s="26">
         <v>65</v>
       </c>
@@ -4506,7 +4650,9 @@
       <c r="A68" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="B68" s="9"/>
+      <c r="B68" s="9" t="s">
+        <v>396</v>
+      </c>
       <c r="C68" s="26">
         <v>66</v>
       </c>
@@ -4528,7 +4674,9 @@
       <c r="A69" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B69" s="9"/>
+      <c r="B69" s="9">
+        <v>66</v>
+      </c>
       <c r="C69" s="26">
         <v>67</v>
       </c>
@@ -4550,7 +4698,9 @@
       <c r="A70" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B70" s="9"/>
+      <c r="B70" s="9" t="s">
+        <v>397</v>
+      </c>
       <c r="C70" s="26">
         <v>68</v>
       </c>
@@ -4572,7 +4722,9 @@
       <c r="A71" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B71" s="9"/>
+      <c r="B71" s="9">
+        <v>68</v>
+      </c>
       <c r="C71" s="26">
         <v>69</v>
       </c>
@@ -4594,7 +4746,9 @@
       <c r="A72" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B72" s="9"/>
+      <c r="B72" s="9">
+        <v>69</v>
+      </c>
       <c r="C72" s="26">
         <v>70</v>
       </c>
@@ -4616,7 +4770,9 @@
       <c r="A73" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B73" s="9"/>
+      <c r="B73" s="9">
+        <v>70</v>
+      </c>
       <c r="C73" s="26">
         <v>71</v>
       </c>
@@ -4638,7 +4794,9 @@
       <c r="A74" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B74" s="9"/>
+      <c r="B74" s="9">
+        <v>71</v>
+      </c>
       <c r="C74" s="26">
         <v>72</v>
       </c>
@@ -4660,7 +4818,9 @@
       <c r="A75" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B75" s="9"/>
+      <c r="B75" s="9">
+        <v>72</v>
+      </c>
       <c r="C75" s="26">
         <v>73</v>
       </c>
@@ -4682,7 +4842,9 @@
       <c r="A76" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B76" s="9"/>
+      <c r="B76" s="9">
+        <v>73</v>
+      </c>
       <c r="C76" s="26">
         <v>74</v>
       </c>
@@ -4704,7 +4866,9 @@
       <c r="A77" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B77" s="9"/>
+      <c r="B77" s="9">
+        <v>74</v>
+      </c>
       <c r="C77" s="26">
         <v>75</v>
       </c>
@@ -4726,7 +4890,9 @@
       <c r="A78" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B78" s="9"/>
+      <c r="B78" s="9">
+        <v>75</v>
+      </c>
       <c r="C78" s="26">
         <v>76</v>
       </c>
@@ -4748,7 +4914,9 @@
       <c r="A79" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B79" s="9"/>
+      <c r="B79" s="9">
+        <v>76</v>
+      </c>
       <c r="C79" s="26">
         <v>77</v>
       </c>
@@ -4770,7 +4938,9 @@
       <c r="A80" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B80" s="9"/>
+      <c r="B80" s="9">
+        <v>2</v>
+      </c>
       <c r="C80" s="26">
         <v>78</v>
       </c>
@@ -4792,7 +4962,9 @@
       <c r="A81" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B81" s="9"/>
+      <c r="B81" s="9">
+        <v>78</v>
+      </c>
       <c r="C81" s="26">
         <v>79</v>
       </c>
@@ -4814,7 +4986,9 @@
       <c r="A82" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B82" s="9"/>
+      <c r="B82" s="9">
+        <v>77</v>
+      </c>
       <c r="C82" s="26">
         <v>80</v>
       </c>
@@ -4836,7 +5010,9 @@
       <c r="A83" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B83" s="9"/>
+      <c r="B83" s="9">
+        <v>67</v>
+      </c>
       <c r="C83" s="26">
         <v>81</v>
       </c>
@@ -4858,7 +5034,9 @@
       <c r="A84" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B84" s="9"/>
+      <c r="B84" s="9">
+        <v>81</v>
+      </c>
       <c r="C84" s="26">
         <v>82</v>
       </c>
@@ -4880,7 +5058,9 @@
       <c r="A85" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B85" s="9"/>
+      <c r="B85" s="9">
+        <v>81</v>
+      </c>
       <c r="C85" s="26">
         <v>83</v>
       </c>
@@ -4902,7 +5082,9 @@
       <c r="A86" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B86" s="9"/>
+      <c r="B86" s="9">
+        <v>76</v>
+      </c>
       <c r="C86" s="26">
         <v>84</v>
       </c>
@@ -4924,7 +5106,9 @@
       <c r="A87" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B87" s="9"/>
+      <c r="B87" s="9">
+        <v>44</v>
+      </c>
       <c r="C87" s="26">
         <v>85</v>
       </c>
@@ -4946,7 +5130,9 @@
       <c r="A88" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B88" s="9"/>
+      <c r="B88" s="9">
+        <v>85</v>
+      </c>
       <c r="C88" s="26">
         <v>86</v>
       </c>
@@ -4968,7 +5154,9 @@
       <c r="A89" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B89" s="9"/>
+      <c r="B89" s="9">
+        <v>67</v>
+      </c>
       <c r="C89" s="26">
         <v>87</v>
       </c>
@@ -4990,7 +5178,9 @@
       <c r="A90" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B90" s="9"/>
+      <c r="B90" s="9">
+        <v>67</v>
+      </c>
       <c r="C90" s="26">
         <v>88</v>
       </c>
@@ -5012,7 +5202,9 @@
       <c r="A91" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="B91" s="26"/>
+      <c r="B91" s="26" t="s">
+        <v>398</v>
+      </c>
       <c r="C91" s="26">
         <v>89</v>
       </c>
@@ -5034,7 +5226,9 @@
       <c r="A92" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="B92" s="29"/>
+      <c r="B92" s="29">
+        <v>89</v>
+      </c>
       <c r="C92" s="26">
         <v>90</v>
       </c>
@@ -5056,7 +5250,9 @@
       <c r="A93" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B93" s="26"/>
+      <c r="B93" s="26">
+        <v>89</v>
+      </c>
       <c r="C93" s="26">
         <v>91</v>
       </c>
@@ -5078,7 +5274,9 @@
       <c r="A94" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B94" s="26"/>
+      <c r="B94" s="26">
+        <v>89</v>
+      </c>
       <c r="C94" s="26">
         <v>92</v>
       </c>
@@ -5100,7 +5298,9 @@
       <c r="A95" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B95" s="26"/>
+      <c r="B95" s="26">
+        <v>89</v>
+      </c>
       <c r="C95" s="26">
         <v>93</v>
       </c>
@@ -5122,7 +5322,9 @@
       <c r="A96" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B96" s="26"/>
+      <c r="B96" s="26">
+        <v>93</v>
+      </c>
       <c r="C96" s="26">
         <v>94</v>
       </c>
@@ -5144,7 +5346,9 @@
       <c r="A97" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B97" s="26"/>
+      <c r="B97" s="26">
+        <v>93</v>
+      </c>
       <c r="C97" s="26">
         <v>95</v>
       </c>
@@ -5166,7 +5370,9 @@
       <c r="A98" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B98" s="26"/>
+      <c r="B98" s="26">
+        <v>93</v>
+      </c>
       <c r="C98" s="26">
         <v>96</v>
       </c>
@@ -5188,7 +5394,9 @@
       <c r="A99" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B99" s="26"/>
+      <c r="B99" s="26">
+        <v>95</v>
+      </c>
       <c r="C99" s="26">
         <v>97</v>
       </c>
@@ -5210,7 +5418,9 @@
       <c r="A100" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B100" s="26"/>
+      <c r="B100" s="26">
+        <v>93</v>
+      </c>
       <c r="C100" s="26">
         <v>98</v>
       </c>
@@ -5232,8 +5442,8 @@
       <c r="A101" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="B101" s="26" t="s">
-        <v>13</v>
+      <c r="B101" s="26">
+        <v>93</v>
       </c>
       <c r="C101" s="26">
         <v>99</v>
@@ -5256,7 +5466,9 @@
       <c r="A102" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="B102" s="29"/>
+      <c r="B102" s="29">
+        <v>98</v>
+      </c>
       <c r="C102" s="26">
         <v>100</v>
       </c>
@@ -5278,7 +5490,9 @@
       <c r="A103" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B103" s="26"/>
+      <c r="B103" s="26">
+        <v>100</v>
+      </c>
       <c r="C103" s="26">
         <v>101</v>
       </c>
@@ -5300,7 +5514,9 @@
       <c r="A104" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B104" s="26"/>
+      <c r="B104" s="26">
+        <v>101</v>
+      </c>
       <c r="C104" s="26">
         <v>102</v>
       </c>
@@ -5322,7 +5538,9 @@
       <c r="A105" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B105" s="26"/>
+      <c r="B105" s="26">
+        <v>102</v>
+      </c>
       <c r="C105" s="26">
         <v>103</v>
       </c>
@@ -5344,7 +5562,9 @@
       <c r="A106" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="B106" s="26"/>
+      <c r="B106" s="26">
+        <v>103</v>
+      </c>
       <c r="C106" s="26">
         <v>104</v>
       </c>
@@ -5366,7 +5586,9 @@
       <c r="A107" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B107" s="26"/>
+      <c r="B107" s="26">
+        <v>104</v>
+      </c>
       <c r="C107" s="26">
         <v>105</v>
       </c>
@@ -5388,7 +5610,9 @@
       <c r="A108" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B108" s="26"/>
+      <c r="B108" s="26">
+        <v>103</v>
+      </c>
       <c r="C108" s="26">
         <v>106</v>
       </c>
@@ -5410,7 +5634,9 @@
       <c r="A109" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B109" s="26"/>
+      <c r="B109" s="26">
+        <v>106</v>
+      </c>
       <c r="C109" s="26">
         <v>107</v>
       </c>
@@ -5432,7 +5658,9 @@
       <c r="A110" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B110" s="26"/>
+      <c r="B110" s="26">
+        <v>106</v>
+      </c>
       <c r="C110" s="26">
         <v>108</v>
       </c>
@@ -5454,7 +5682,9 @@
       <c r="A111" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="26"/>
+      <c r="B111" s="26">
+        <v>106</v>
+      </c>
       <c r="C111" s="26">
         <v>109</v>
       </c>
@@ -5476,7 +5706,9 @@
       <c r="A112" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B112" s="36"/>
+      <c r="B112" s="36" t="s">
+        <v>399</v>
+      </c>
       <c r="C112" s="26">
         <v>110</v>
       </c>
@@ -5498,7 +5730,9 @@
       <c r="A113" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B113" s="36"/>
+      <c r="B113" s="36">
+        <v>110</v>
+      </c>
       <c r="C113" s="26">
         <v>111</v>
       </c>
@@ -5520,7 +5754,9 @@
       <c r="A114" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B114" s="36"/>
+      <c r="B114" s="36">
+        <v>110</v>
+      </c>
       <c r="C114" s="26">
         <v>112</v>
       </c>
@@ -5542,7 +5778,9 @@
       <c r="A115" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B115" s="36"/>
+      <c r="B115" s="36">
+        <v>112</v>
+      </c>
       <c r="C115" s="26">
         <v>113</v>
       </c>
@@ -5564,7 +5802,9 @@
       <c r="A116" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B116" s="36"/>
+      <c r="B116" s="36">
+        <v>112</v>
+      </c>
       <c r="C116" s="26">
         <v>114</v>
       </c>
@@ -5586,7 +5826,9 @@
       <c r="A117" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B117" s="36"/>
+      <c r="B117" s="36">
+        <v>112</v>
+      </c>
       <c r="C117" s="26">
         <v>115</v>
       </c>
@@ -5608,7 +5850,9 @@
       <c r="A118" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B118" s="36"/>
+      <c r="B118" s="36">
+        <v>115</v>
+      </c>
       <c r="C118" s="26">
         <v>116</v>
       </c>
@@ -5628,7 +5872,9 @@
       <c r="A119" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B119" s="36"/>
+      <c r="B119" s="36">
+        <v>116</v>
+      </c>
       <c r="C119" s="26">
         <v>117</v>
       </c>
@@ -5650,7 +5896,9 @@
       <c r="A120" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B120" s="36"/>
+      <c r="B120" s="36">
+        <v>116</v>
+      </c>
       <c r="C120" s="26">
         <v>118</v>
       </c>
@@ -5672,7 +5920,9 @@
       <c r="A121" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B121" s="36"/>
+      <c r="B121" s="36">
+        <v>116</v>
+      </c>
       <c r="C121" s="26">
         <v>119</v>
       </c>
@@ -5694,7 +5944,9 @@
       <c r="A122" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B122" s="36"/>
+      <c r="B122" s="36">
+        <v>116</v>
+      </c>
       <c r="C122" s="26">
         <v>120</v>
       </c>
@@ -5716,7 +5968,9 @@
       <c r="A123" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B123" s="36"/>
+      <c r="B123" s="36">
+        <v>116</v>
+      </c>
       <c r="C123" s="26">
         <v>121</v>
       </c>
@@ -5738,7 +5992,9 @@
       <c r="A124" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B124" s="36"/>
+      <c r="B124" s="36">
+        <v>116</v>
+      </c>
       <c r="C124" s="26">
         <v>122</v>
       </c>
@@ -5760,7 +6016,9 @@
       <c r="A125" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B125" s="36"/>
+      <c r="B125" s="36">
+        <v>116</v>
+      </c>
       <c r="C125" s="26">
         <v>123</v>
       </c>
@@ -5782,7 +6040,9 @@
       <c r="A126" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B126" s="36"/>
+      <c r="B126" s="36">
+        <v>116</v>
+      </c>
       <c r="C126" s="26">
         <v>124</v>
       </c>
@@ -5804,7 +6064,9 @@
       <c r="A127" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B127" s="36"/>
+      <c r="B127" s="36">
+        <v>116</v>
+      </c>
       <c r="C127" s="26">
         <v>125</v>
       </c>
@@ -5826,7 +6088,9 @@
       <c r="A128" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B128" s="36"/>
+      <c r="B128" s="36">
+        <v>116</v>
+      </c>
       <c r="C128" s="26">
         <v>126</v>
       </c>
@@ -5848,7 +6112,9 @@
       <c r="A129" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B129" s="36"/>
+      <c r="B129" s="36">
+        <v>116</v>
+      </c>
       <c r="C129" s="26">
         <v>127</v>
       </c>
@@ -5870,7 +6136,9 @@
       <c r="A130" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B130" s="36"/>
+      <c r="B130" s="36">
+        <v>116</v>
+      </c>
       <c r="C130" s="26">
         <v>128</v>
       </c>
@@ -5892,7 +6160,9 @@
       <c r="A131" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B131" s="36"/>
+      <c r="B131" s="36">
+        <v>116</v>
+      </c>
       <c r="C131" s="26">
         <v>129</v>
       </c>
@@ -5914,7 +6184,9 @@
       <c r="A132" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B132" s="36"/>
+      <c r="B132" s="36">
+        <v>116</v>
+      </c>
       <c r="C132" s="26">
         <v>130</v>
       </c>
@@ -5936,7 +6208,9 @@
       <c r="A133" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B133" s="36"/>
+      <c r="B133" s="36">
+        <v>116</v>
+      </c>
       <c r="C133" s="26">
         <v>131</v>
       </c>
@@ -5958,7 +6232,9 @@
       <c r="A134" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B134" s="36"/>
+      <c r="B134" s="36">
+        <v>116</v>
+      </c>
       <c r="C134" s="26">
         <v>132</v>
       </c>
@@ -5980,7 +6256,9 @@
       <c r="A135" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B135" s="36"/>
+      <c r="B135" s="36">
+        <v>116</v>
+      </c>
       <c r="C135" s="26">
         <v>133</v>
       </c>
@@ -6002,7 +6280,9 @@
       <c r="A136" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B136" s="36"/>
+      <c r="B136" s="36">
+        <v>116</v>
+      </c>
       <c r="C136" s="26">
         <v>134</v>
       </c>
@@ -6024,7 +6304,9 @@
       <c r="A137" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B137" s="36"/>
+      <c r="B137" s="36">
+        <v>134</v>
+      </c>
       <c r="C137" s="26">
         <v>135</v>
       </c>
@@ -6046,7 +6328,9 @@
       <c r="A138" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B138" s="36"/>
+      <c r="B138" s="36">
+        <v>135</v>
+      </c>
       <c r="C138" s="26">
         <v>136</v>
       </c>
@@ -6068,7 +6352,9 @@
       <c r="A139" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B139" s="36"/>
+      <c r="B139" s="36">
+        <v>136</v>
+      </c>
       <c r="C139" s="26">
         <v>137</v>
       </c>
@@ -6090,7 +6376,9 @@
       <c r="A140" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B140" s="36"/>
+      <c r="B140" s="36">
+        <v>137</v>
+      </c>
       <c r="C140" s="26">
         <v>138</v>
       </c>
@@ -6112,7 +6400,9 @@
       <c r="A141" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B141" s="36"/>
+      <c r="B141" s="36">
+        <v>116</v>
+      </c>
       <c r="C141" s="26">
         <v>139</v>
       </c>
@@ -6134,7 +6424,9 @@
       <c r="A142" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B142" s="36"/>
+      <c r="B142" s="36">
+        <v>139</v>
+      </c>
       <c r="C142" s="26">
         <v>140</v>
       </c>
@@ -6156,7 +6448,9 @@
       <c r="A143" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B143" s="36"/>
+      <c r="B143" s="36">
+        <v>137</v>
+      </c>
       <c r="C143" s="26">
         <v>141</v>
       </c>
@@ -6178,7 +6472,9 @@
       <c r="A144" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B144" s="36"/>
+      <c r="B144" s="36">
+        <v>141</v>
+      </c>
       <c r="C144" s="26">
         <v>142</v>
       </c>
@@ -6200,7 +6496,9 @@
       <c r="A145" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B145" s="36"/>
+      <c r="B145" s="36">
+        <v>142</v>
+      </c>
       <c r="C145" s="26">
         <v>143</v>
       </c>
@@ -6222,7 +6520,9 @@
       <c r="A146" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B146" s="36"/>
+      <c r="B146" s="36">
+        <v>143</v>
+      </c>
       <c r="C146" s="26">
         <v>144</v>
       </c>
@@ -6244,7 +6544,9 @@
       <c r="A147" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B147" s="36"/>
+      <c r="B147" s="36">
+        <v>116</v>
+      </c>
       <c r="C147" s="26">
         <v>145</v>
       </c>
@@ -6266,7 +6568,9 @@
       <c r="A148" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B148" s="36"/>
+      <c r="B148" s="36">
+        <v>137</v>
+      </c>
       <c r="C148" s="26">
         <v>146</v>
       </c>
@@ -6288,7 +6592,9 @@
       <c r="A149" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="B149" s="36"/>
+      <c r="B149" s="36">
+        <v>137</v>
+      </c>
       <c r="C149" s="36">
         <v>147</v>
       </c>
@@ -6310,7 +6616,9 @@
       <c r="A150" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="B150" s="26"/>
+      <c r="B150" s="26">
+        <v>110</v>
+      </c>
       <c r="C150" s="29">
         <v>148</v>
       </c>
@@ -6334,7 +6642,9 @@
       <c r="A151" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="B151" s="26"/>
+      <c r="B151" s="26">
+        <v>116</v>
+      </c>
       <c r="C151" s="29">
         <v>149</v>
       </c>
@@ -6356,7 +6666,9 @@
       <c r="A152" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="B152" s="26"/>
+      <c r="B152" s="26">
+        <v>116</v>
+      </c>
       <c r="C152" s="29">
         <v>150</v>
       </c>
@@ -6806,7 +7118,9 @@
       <c r="D2" s="43" t="s">
         <v>371</v>
       </c>
-      <c r="E2" s="7"/>
+      <c r="E2" s="7" t="s">
+        <v>400</v>
+      </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -6841,7 +7155,9 @@
       <c r="D3" s="43" t="s">
         <v>355</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="7">
+        <v>4</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -6876,7 +7192,9 @@
       <c r="D4" s="45" t="s">
         <v>358</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7">
+        <v>57</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -6911,7 +7229,9 @@
       <c r="D5" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="7">
+        <v>56</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -6946,7 +7266,9 @@
       <c r="D6" s="46" t="s">
         <v>364</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="7">
+        <v>47</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -6981,7 +7303,9 @@
       <c r="D7" s="43" t="s">
         <v>367</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="7">
+        <v>62</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -7016,7 +7340,9 @@
       <c r="D8" s="47" t="s">
         <v>370</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>401</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
